--- a/Chennai-May-2025.xlsx
+++ b/Chennai-May-2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="48">
   <si>
     <t>Sr. No</t>
   </si>
@@ -94,6 +94,9 @@
     <t>Profit %</t>
   </si>
   <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
     <t>Chennai</t>
   </si>
   <si>
@@ -133,22 +136,37 @@
     <t>TN14AK9389</t>
   </si>
   <si>
-    <t>Etios</t>
-  </si>
-  <si>
-    <t>Crysta</t>
-  </si>
-  <si>
-    <t>Citron</t>
-  </si>
-  <si>
-    <t>-</t>
+    <t>ETIOS</t>
+  </si>
+  <si>
+    <t>CRYSTA</t>
+  </si>
+  <si>
+    <t>CITROEN</t>
+  </si>
+  <si>
+    <t>29/05/2018</t>
+  </si>
+  <si>
+    <t>27/06/2019</t>
+  </si>
+  <si>
+    <t>16/09/2019</t>
+  </si>
+  <si>
+    <t>26/02/2024</t>
+  </si>
+  <si>
+    <t>29/07/2024</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -201,11 +219,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -500,10 +519,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z12"/>
+  <dimension ref="A1:AA12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -582,28 +601,31 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:27">
       <c r="A2">
         <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>2025</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G2" t="s">
-        <v>42</v>
+        <v>40</v>
+      </c>
+      <c r="G2" s="2">
+        <v>42744</v>
       </c>
       <c r="H2">
         <v>331447</v>
@@ -663,27 +685,27 @@
         <v>49.58</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:27">
       <c r="A3">
         <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>2025</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H3">
         <v>148471</v>
@@ -743,27 +765,27 @@
         <v>61.03</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:27">
       <c r="A4">
         <v>53</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>2025</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G4" t="s">
-        <v>42</v>
+        <v>41</v>
+      </c>
+      <c r="G4" s="2">
+        <v>43350</v>
       </c>
       <c r="H4">
         <v>181018</v>
@@ -823,27 +845,27 @@
         <v>-13.88</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:27">
       <c r="A5">
         <v>54</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5">
         <v>2025</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G5">
-        <v>44874</v>
+        <v>41</v>
+      </c>
+      <c r="G5" s="2">
+        <v>44815</v>
       </c>
       <c r="H5">
         <v>93983</v>
@@ -903,27 +925,27 @@
         <v>56.84</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:27">
       <c r="A6">
         <v>55</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6">
         <v>2025</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6">
-        <v>44874</v>
+        <v>41</v>
+      </c>
+      <c r="G6" s="2">
+        <v>44815</v>
       </c>
       <c r="H6">
         <v>98700</v>
@@ -983,27 +1005,27 @@
         <v>63.23</v>
       </c>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:27">
       <c r="A7">
         <v>56</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7">
         <v>2025</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G7">
-        <v>44874</v>
+        <v>41</v>
+      </c>
+      <c r="G7" s="2">
+        <v>44815</v>
       </c>
       <c r="H7">
         <v>118673</v>
@@ -1063,27 +1085,27 @@
         <v>62.81</v>
       </c>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:27">
       <c r="A8">
         <v>57</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8">
         <v>2025</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8">
-        <v>43643</v>
+        <v>41</v>
+      </c>
+      <c r="G8" t="s">
+        <v>44</v>
       </c>
       <c r="H8">
         <v>118105</v>
@@ -1143,27 +1165,27 @@
         <v>57.72</v>
       </c>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:27">
       <c r="A9">
         <v>58</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9">
         <v>2025</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H9">
         <v>167084</v>
@@ -1223,27 +1245,27 @@
         <v>44.08</v>
       </c>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:27">
       <c r="A10">
         <v>59</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10">
         <v>2025</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
-        <v>40</v>
-      </c>
-      <c r="G10">
-        <v>43724</v>
+        <v>41</v>
+      </c>
+      <c r="G10" t="s">
+        <v>45</v>
       </c>
       <c r="H10">
         <v>99924</v>
@@ -1303,27 +1325,27 @@
         <v>59.96</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:27">
       <c r="A11">
         <v>60</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <v>2025</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>40</v>
-      </c>
-      <c r="G11">
-        <v>45348</v>
+        <v>41</v>
+      </c>
+      <c r="G11" t="s">
+        <v>46</v>
       </c>
       <c r="H11">
         <v>45266</v>
@@ -1383,27 +1405,27 @@
         <v>38.36</v>
       </c>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:27">
       <c r="A12">
         <v>61</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>2025</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>41</v>
-      </c>
-      <c r="G12">
-        <v>45502</v>
+        <v>42</v>
+      </c>
+      <c r="G12" t="s">
+        <v>47</v>
       </c>
       <c r="H12">
         <v>17894</v>
